--- a/Caracterizacion_Haces/data/z8mm-822.xlsx
+++ b/Caracterizacion_Haces/data/z8mm-822.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="171">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,382 +128,415 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-803,8</t>
-  </si>
-  <si>
-    <t>58,09</t>
-  </si>
-  <si>
-    <t>60,83</t>
-  </si>
-  <si>
-    <t>65,54</t>
-  </si>
-  <si>
-    <t>52,73</t>
-  </si>
-  <si>
-    <t>57,64</t>
-  </si>
-  <si>
-    <t>61,21</t>
+    <t>749,0</t>
+  </si>
+  <si>
+    <t>59,35</t>
+  </si>
+  <si>
+    <t>63,57</t>
+  </si>
+  <si>
+    <t>71,06</t>
+  </si>
+  <si>
+    <t>50,15</t>
+  </si>
+  <si>
+    <t>59,43</t>
+  </si>
+  <si>
+    <t>62,27</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>-804,6</t>
-  </si>
-  <si>
-    <t>58,06</t>
-  </si>
-  <si>
-    <t>60,74</t>
-  </si>
-  <si>
-    <t>52,58</t>
-  </si>
-  <si>
-    <t>58,00</t>
-  </si>
-  <si>
-    <t>61,22</t>
+    <t>750,6</t>
+  </si>
+  <si>
+    <t>59,77</t>
+  </si>
+  <si>
+    <t>63,71</t>
+  </si>
+  <si>
+    <t>70,63</t>
+  </si>
+  <si>
+    <t>51,40</t>
+  </si>
+  <si>
+    <t>59,62</t>
+  </si>
+  <si>
+    <t>62,18</t>
   </si>
   <si>
     <t>0,4</t>
   </si>
   <si>
-    <t>58,16</t>
-  </si>
-  <si>
-    <t>60,64</t>
-  </si>
-  <si>
-    <t>64,94</t>
-  </si>
-  <si>
-    <t>53,31</t>
-  </si>
-  <si>
-    <t>57,60</t>
-  </si>
-  <si>
-    <t>61,00</t>
+    <t>748,5</t>
+  </si>
+  <si>
+    <t>59,85</t>
+  </si>
+  <si>
+    <t>63,37</t>
+  </si>
+  <si>
+    <t>70,84</t>
+  </si>
+  <si>
+    <t>50,80</t>
+  </si>
+  <si>
+    <t>59,37</t>
+  </si>
+  <si>
+    <t>62,52</t>
   </si>
   <si>
     <t>0,6</t>
   </si>
   <si>
-    <t>-803,5</t>
-  </si>
-  <si>
-    <t>57,80</t>
-  </si>
-  <si>
-    <t>60,79</t>
-  </si>
-  <si>
-    <t>65,24</t>
-  </si>
-  <si>
-    <t>52,72</t>
-  </si>
-  <si>
-    <t>57,54</t>
-  </si>
-  <si>
-    <t>61,31</t>
+    <t>749,6</t>
+  </si>
+  <si>
+    <t>59,59</t>
+  </si>
+  <si>
+    <t>63,43</t>
+  </si>
+  <si>
+    <t>70,67</t>
+  </si>
+  <si>
+    <t>50,79</t>
+  </si>
+  <si>
+    <t>62,59</t>
   </si>
   <si>
     <t>0,8</t>
   </si>
   <si>
-    <t>57,84</t>
-  </si>
-  <si>
-    <t>60,52</t>
-  </si>
-  <si>
-    <t>52,47</t>
-  </si>
-  <si>
-    <t>58,04</t>
-  </si>
-  <si>
-    <t>61,38</t>
+    <t>748,2</t>
+  </si>
+  <si>
+    <t>60,24</t>
+  </si>
+  <si>
+    <t>62,81</t>
+  </si>
+  <si>
+    <t>70,37</t>
+  </si>
+  <si>
+    <t>51,21</t>
+  </si>
+  <si>
+    <t>59,21</t>
   </si>
   <si>
     <t>1,0</t>
   </si>
   <si>
-    <t>60,76</t>
-  </si>
-  <si>
-    <t>65,38</t>
-  </si>
-  <si>
-    <t>52,55</t>
-  </si>
-  <si>
-    <t>57,69</t>
-  </si>
-  <si>
-    <t>61,11</t>
+    <t>62,73</t>
+  </si>
+  <si>
+    <t>70,38</t>
+  </si>
+  <si>
+    <t>50,64</t>
+  </si>
+  <si>
+    <t>59,25</t>
+  </si>
+  <si>
+    <t>62,31</t>
   </si>
   <si>
     <t>1,2</t>
   </si>
   <si>
-    <t>-803,2</t>
-  </si>
-  <si>
-    <t>57,72</t>
-  </si>
-  <si>
-    <t>60,92</t>
-  </si>
-  <si>
-    <t>65,48</t>
-  </si>
-  <si>
-    <t>52,49</t>
-  </si>
-  <si>
-    <t>57,99</t>
-  </si>
-  <si>
-    <t>61,35</t>
+    <t>59,82</t>
+  </si>
+  <si>
+    <t>63,49</t>
+  </si>
+  <si>
+    <t>70,57</t>
+  </si>
+  <si>
+    <t>51,29</t>
+  </si>
+  <si>
+    <t>59,53</t>
+  </si>
+  <si>
+    <t>62,42</t>
   </si>
   <si>
     <t>1,4</t>
   </si>
   <si>
-    <t>-804,3</t>
-  </si>
-  <si>
-    <t>57,78</t>
-  </si>
-  <si>
-    <t>60,85</t>
-  </si>
-  <si>
-    <t>65,28</t>
-  </si>
-  <si>
-    <t>57,61</t>
-  </si>
-  <si>
-    <t>60,97</t>
+    <t>59,89</t>
+  </si>
+  <si>
+    <t>62,74</t>
+  </si>
+  <si>
+    <t>70,83</t>
+  </si>
+  <si>
+    <t>50,06</t>
+  </si>
+  <si>
+    <t>59,15</t>
+  </si>
+  <si>
+    <t>62,24</t>
   </si>
   <si>
     <t>1,6</t>
   </si>
   <si>
-    <t>57,79</t>
-  </si>
-  <si>
-    <t>60,59</t>
-  </si>
-  <si>
-    <t>65,78</t>
-  </si>
-  <si>
-    <t>51,81</t>
-  </si>
-  <si>
-    <t>57,73</t>
-  </si>
-  <si>
-    <t>60,96</t>
+    <t>749,8</t>
+  </si>
+  <si>
+    <t>63,24</t>
+  </si>
+  <si>
+    <t>70,79</t>
+  </si>
+  <si>
+    <t>50,43</t>
+  </si>
+  <si>
+    <t>59,26</t>
+  </si>
+  <si>
+    <t>62,47</t>
   </si>
   <si>
     <t>1,8</t>
   </si>
   <si>
-    <t>57,68</t>
-  </si>
-  <si>
-    <t>60,63</t>
-  </si>
-  <si>
-    <t>64,86</t>
-  </si>
-  <si>
-    <t>52,88</t>
-  </si>
-  <si>
-    <t>57,74</t>
-  </si>
-  <si>
-    <t>61,40</t>
+    <t>750,4</t>
+  </si>
+  <si>
+    <t>59,71</t>
+  </si>
+  <si>
+    <t>62,63</t>
+  </si>
+  <si>
+    <t>70,68</t>
+  </si>
+  <si>
+    <t>49,92</t>
+  </si>
+  <si>
+    <t>59,47</t>
+  </si>
+  <si>
+    <t>62,12</t>
   </si>
   <si>
     <t>2,0</t>
   </si>
   <si>
-    <t>57,77</t>
-  </si>
-  <si>
-    <t>60,56</t>
-  </si>
-  <si>
-    <t>65,21</t>
-  </si>
-  <si>
-    <t>52,46</t>
-  </si>
-  <si>
-    <t>61,34</t>
+    <t>750,1</t>
+  </si>
+  <si>
+    <t>60,09</t>
+  </si>
+  <si>
+    <t>62,85</t>
+  </si>
+  <si>
+    <t>70,35</t>
+  </si>
+  <si>
+    <t>51,10</t>
+  </si>
+  <si>
+    <t>62,23</t>
   </si>
   <si>
     <t>2,2</t>
   </si>
   <si>
-    <t>60,69</t>
-  </si>
-  <si>
-    <t>65,36</t>
-  </si>
-  <si>
-    <t>52,51</t>
-  </si>
-  <si>
-    <t>61,26</t>
+    <t>59,86</t>
+  </si>
+  <si>
+    <t>62,67</t>
+  </si>
+  <si>
+    <t>70,61</t>
+  </si>
+  <si>
+    <t>50,25</t>
+  </si>
+  <si>
+    <t>59,40</t>
+  </si>
+  <si>
+    <t>62,58</t>
   </si>
   <si>
     <t>2,4</t>
   </si>
   <si>
-    <t>-804,0</t>
-  </si>
-  <si>
-    <t>57,91</t>
-  </si>
-  <si>
-    <t>60,80</t>
-  </si>
-  <si>
-    <t>52,85</t>
-  </si>
-  <si>
-    <t>57,83</t>
-  </si>
-  <si>
-    <t>61,37</t>
+    <t>59,69</t>
+  </si>
+  <si>
+    <t>63,07</t>
+  </si>
+  <si>
+    <t>70,32</t>
+  </si>
+  <si>
+    <t>50,96</t>
+  </si>
+  <si>
+    <t>62,11</t>
   </si>
   <si>
     <t>2,6</t>
   </si>
   <si>
-    <t>57,85</t>
-  </si>
-  <si>
-    <t>60,51</t>
-  </si>
-  <si>
-    <t>52,28</t>
+    <t>60,20</t>
+  </si>
+  <si>
+    <t>70,58</t>
+  </si>
+  <si>
+    <t>50,58</t>
+  </si>
+  <si>
+    <t>59,46</t>
+  </si>
+  <si>
+    <t>62,15</t>
   </si>
   <si>
     <t>2,8</t>
   </si>
   <si>
-    <t>58,01</t>
-  </si>
-  <si>
-    <t>60,75</t>
-  </si>
-  <si>
-    <t>65,08</t>
-  </si>
-  <si>
-    <t>53,10</t>
-  </si>
-  <si>
-    <t>57,90</t>
-  </si>
-  <si>
-    <t>61,41</t>
+    <t>60,31</t>
+  </si>
+  <si>
+    <t>62,68</t>
+  </si>
+  <si>
+    <t>70,72</t>
   </si>
   <si>
     <t>3,0</t>
   </si>
   <si>
-    <t>57,88</t>
-  </si>
-  <si>
-    <t>64,95</t>
-  </si>
-  <si>
-    <t>53,18</t>
-  </si>
-  <si>
-    <t>57,66</t>
-  </si>
-  <si>
-    <t>61,28</t>
+    <t>59,94</t>
+  </si>
+  <si>
+    <t>63,26</t>
+  </si>
+  <si>
+    <t>70,91</t>
+  </si>
+  <si>
+    <t>50,66</t>
+  </si>
+  <si>
+    <t>59,33</t>
+  </si>
+  <si>
+    <t>62,33</t>
   </si>
   <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>-805,4</t>
-  </si>
-  <si>
-    <t>52,98</t>
-  </si>
-  <si>
-    <t>57,95</t>
+    <t>59,98</t>
+  </si>
+  <si>
+    <t>63,87</t>
+  </si>
+  <si>
+    <t>70,98</t>
+  </si>
+  <si>
+    <t>51,36</t>
+  </si>
+  <si>
+    <t>59,50</t>
+  </si>
+  <si>
+    <t>62,21</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>57,70</t>
-  </si>
-  <si>
-    <t>65,14</t>
-  </si>
-  <si>
-    <t>52,68</t>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>62,82</t>
+  </si>
+  <si>
+    <t>70,20</t>
+  </si>
+  <si>
+    <t>51,18</t>
+  </si>
+  <si>
+    <t>59,54</t>
+  </si>
+  <si>
+    <t>62,34</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>-802,7</t>
-  </si>
-  <si>
-    <t>57,81</t>
-  </si>
-  <si>
-    <t>60,60</t>
-  </si>
-  <si>
-    <t>65,61</t>
-  </si>
-  <si>
-    <t>52,06</t>
-  </si>
-  <si>
-    <t>61,02</t>
+    <t>59,97</t>
+  </si>
+  <si>
+    <t>62,91</t>
+  </si>
+  <si>
+    <t>70,95</t>
+  </si>
+  <si>
+    <t>50,22</t>
+  </si>
+  <si>
+    <t>59,17</t>
+  </si>
+  <si>
+    <t>62,22</t>
   </si>
   <si>
     <t>3,8</t>
   </si>
   <si>
-    <t>57,76</t>
-  </si>
-  <si>
-    <t>60,73</t>
-  </si>
-  <si>
-    <t>65,29</t>
-  </si>
-  <si>
-    <t>57,71</t>
-  </si>
-  <si>
-    <t>61,03</t>
+    <t>750,9</t>
+  </si>
+  <si>
+    <t>60,02</t>
+  </si>
+  <si>
+    <t>62,56</t>
+  </si>
+  <si>
+    <t>70,43</t>
+  </si>
+  <si>
+    <t>50,55</t>
+  </si>
+  <si>
+    <t>59,45</t>
   </si>
 </sst>
 </file>
@@ -844,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -852,7 +885,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59432870370370372</v>
+        <v>0.77115740740740746</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -993,7 +1026,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2650</v>
+        <v>1060</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1022,7 +1055,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2649</v>
+        <v>1061</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -1031,172 +1064,172 @@
         <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C25">
-        <v>2647</v>
+        <v>1059</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26">
+        <v>1060</v>
+      </c>
+      <c r="D26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26">
-        <v>2648</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" t="s">
-        <v>61</v>
-      </c>
       <c r="I26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C27">
-        <v>2648</v>
+        <v>1057</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H27" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I27" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
       <c r="C28">
-        <v>2651</v>
+        <v>1058</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C29">
-        <v>2650</v>
+        <v>1058</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="C30">
-        <v>2651</v>
+        <v>1059</v>
       </c>
       <c r="D30" t="s">
         <v>85</v>
@@ -1208,361 +1241,361 @@
         <v>87</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="C31">
-        <v>2649</v>
+        <v>1057</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="C32">
-        <v>2649</v>
+        <v>1060</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C33">
-        <v>2647</v>
+        <v>1059</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H33" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C34">
-        <v>2651</v>
+        <v>1059</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C35">
-        <v>2649</v>
+        <v>1059</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="I35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C36">
-        <v>2650</v>
+        <v>1061</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H36" t="s">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="I36" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C37">
-        <v>2650</v>
+        <v>1059</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C38">
-        <v>2648</v>
+        <v>1060</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F38" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H38" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I38" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>2650</v>
+        <v>1061</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="F39" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G39" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H39" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I39" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C40">
-        <v>2650</v>
+        <v>1060</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="F40" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G40" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H40" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="C41">
-        <v>2651</v>
+        <v>1061</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F41" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G41" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H41" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="I41" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="C42">
-        <v>2650</v>
+        <v>1060</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E42" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="H42" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I42" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
